--- a/Group12Presentation_market_segmentation_data_Charts_Analysis.xlsx
+++ b/Group12Presentation_market_segmentation_data_Charts_Analysis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guscanada-my.sharepoint.com/personal/bimbo_solanke9888_myunfc_ca/Documents/MA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B44151BF-3EFD-9B46-8CD6-CB4D361207C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A825CB6F-8A40-A54A-A41E-5E27948D53AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40660,16 +40660,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7F1279D-4B79-47CF-B8E9-26E58F421CE3}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="37e8a054-c3ef-4ef6-bc24-8e81f835a26f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="37e8a054-c3ef-4ef6-bc24-8e81f835a26f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="1f9ef79d-73e0-4e80-a94e-bca4aac6ae19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>